--- a/DOCS/PPROG-25_26-DiagramaGantt-I4.xlsx
+++ b/DOCS/PPROG-25_26-DiagramaGantt-I4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\608jo\Documents\GitHub\PPROGF\DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB599BE6-D623-4205-AC97-E3E32C616165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2999CB6-5927-4C5B-B21F-9F0C3712F48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,7 +726,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -839,6 +839,57 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -857,55 +908,7 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,80 +1186,80 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="58"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="42" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42" t="s">
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42" t="s">
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42" t="s">
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="42"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="59"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="39"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1343,22 +1346,22 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="44"/>
+      <c r="H7" s="38"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="11"/>
-      <c r="M7" s="44"/>
+      <c r="M7" s="38"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
       <c r="Q7" s="11"/>
-      <c r="R7" s="44"/>
+      <c r="R7" s="38"/>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
       <c r="V7" s="11"/>
-      <c r="W7" s="44"/>
+      <c r="W7" s="38"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
       <c r="Z7" s="10"/>
@@ -1377,22 +1380,22 @@
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="45"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="18"/>
-      <c r="M8" s="45"/>
+      <c r="M8" s="39"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="18"/>
-      <c r="R8" s="45"/>
+      <c r="R8" s="39"/>
       <c r="S8" s="17"/>
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
       <c r="V8" s="18"/>
-      <c r="W8" s="45"/>
+      <c r="W8" s="39"/>
       <c r="X8" s="17"/>
       <c r="Y8" s="17"/>
       <c r="Z8" s="17"/>
@@ -1411,22 +1414,22 @@
       <c r="G9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="46"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="18"/>
-      <c r="M9" s="46"/>
+      <c r="M9" s="40"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="18"/>
-      <c r="R9" s="46"/>
+      <c r="R9" s="40"/>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
       <c r="U9" s="17"/>
       <c r="V9" s="18"/>
-      <c r="W9" s="46"/>
+      <c r="W9" s="40"/>
       <c r="X9" s="17"/>
       <c r="Y9" s="17"/>
       <c r="Z9" s="17"/>
@@ -1445,22 +1448,22 @@
       <c r="G10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="46"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="18"/>
-      <c r="M10" s="46"/>
+      <c r="M10" s="40"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
       <c r="Q10" s="18"/>
-      <c r="R10" s="46"/>
+      <c r="R10" s="40"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
       <c r="U10" s="17"/>
       <c r="V10" s="18"/>
-      <c r="W10" s="46"/>
+      <c r="W10" s="40"/>
       <c r="X10" s="17"/>
       <c r="Y10" s="17"/>
       <c r="Z10" s="17"/>
@@ -1479,23 +1482,23 @@
       <c r="G11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="57"/>
-      <c r="I11" s="56"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="50"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="18"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="56"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="18"/>
-      <c r="R11" s="57"/>
-      <c r="S11" s="56"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="50"/>
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
       <c r="V11" s="18"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="56"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="50"/>
       <c r="Y11" s="17"/>
       <c r="Z11" s="17"/>
       <c r="AA11" s="18"/>
@@ -1513,23 +1516,23 @@
       <c r="G12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="57"/>
-      <c r="I12" s="56"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="50"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="18"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="56"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="50"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
       <c r="Q12" s="18"/>
-      <c r="R12" s="57"/>
-      <c r="S12" s="56"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="50"/>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
       <c r="V12" s="18"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="56"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="50"/>
       <c r="Y12" s="17"/>
       <c r="Z12" s="17"/>
       <c r="AA12" s="18"/>
@@ -1570,8 +1573,8 @@
       <c r="V13" s="18"/>
       <c r="W13" s="16"/>
       <c r="X13" s="17"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="48"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="42"/>
       <c r="AA13" s="18"/>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.3">
@@ -1610,8 +1613,8 @@
       <c r="V14" s="18"/>
       <c r="W14" s="16"/>
       <c r="X14" s="17"/>
-      <c r="Y14" s="48"/>
-      <c r="Z14" s="48"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="42"/>
       <c r="AA14" s="18"/>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.3">
@@ -1650,8 +1653,8 @@
       <c r="V15" s="18"/>
       <c r="W15" s="16"/>
       <c r="X15" s="17"/>
-      <c r="Y15" s="48"/>
-      <c r="Z15" s="48"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
       <c r="AA15" s="18"/>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.3">
@@ -1672,7 +1675,7 @@
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="58"/>
+      <c r="M16" s="52"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
@@ -1707,7 +1710,7 @@
       <c r="K17" s="17"/>
       <c r="L17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="59"/>
+      <c r="N17" s="53"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="18"/>
@@ -1741,7 +1744,7 @@
       <c r="K18" s="17"/>
       <c r="L18" s="18"/>
       <c r="M18" s="16"/>
-      <c r="N18" s="59"/>
+      <c r="N18" s="53"/>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
       <c r="Q18" s="18"/>
@@ -1779,7 +1782,7 @@
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
       <c r="Q19" s="18"/>
-      <c r="R19" s="16"/>
+      <c r="R19" s="52"/>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
@@ -1813,12 +1816,12 @@
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
       <c r="Q20" s="18"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="59"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="53"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
       <c r="V20" s="18"/>
-      <c r="W20" s="16"/>
+      <c r="W20" s="52"/>
       <c r="X20" s="17"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="17"/>
@@ -1842,7 +1845,7 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="18"/>
-      <c r="M21" s="55"/>
+      <c r="M21" s="49"/>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
@@ -1875,7 +1878,7 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
-      <c r="L22" s="47"/>
+      <c r="L22" s="41"/>
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
@@ -1910,8 +1913,8 @@
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="18"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="53"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="47"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
       <c r="Q23" s="18"/>
@@ -1945,7 +1948,7 @@
       <c r="K24" s="17"/>
       <c r="L24" s="18"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="53"/>
+      <c r="N24" s="47"/>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
       <c r="Q24" s="18"/>
@@ -1978,7 +1981,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
       <c r="L25" s="18"/>
-      <c r="M25" s="45"/>
+      <c r="M25" s="39"/>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
@@ -2012,7 +2015,7 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="18"/>
-      <c r="M26" s="45"/>
+      <c r="M26" s="39"/>
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
@@ -2047,7 +2050,7 @@
       <c r="K27" s="17"/>
       <c r="L27" s="18"/>
       <c r="M27" s="16"/>
-      <c r="N27" s="49"/>
+      <c r="N27" s="43"/>
       <c r="O27" s="17"/>
       <c r="P27" s="17"/>
       <c r="Q27" s="18"/>
@@ -2083,8 +2086,8 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
       <c r="O28" s="17"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="47"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="41"/>
       <c r="R28" s="16"/>
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
@@ -2120,9 +2123,9 @@
       <c r="N29" s="17"/>
       <c r="O29" s="17"/>
       <c r="P29" s="17"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="51"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="45"/>
       <c r="T29" s="17"/>
       <c r="U29" s="17"/>
       <c r="V29" s="18"/>
@@ -2158,7 +2161,7 @@
       <c r="P30" s="17"/>
       <c r="Q30" s="18"/>
       <c r="R30" s="16"/>
-      <c r="S30" s="49"/>
+      <c r="S30" s="43"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
       <c r="V30" s="18"/>
@@ -2196,8 +2199,8 @@
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
       <c r="V31" s="18"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="49"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="43"/>
       <c r="Y31" s="17"/>
       <c r="Z31" s="17"/>
       <c r="AA31" s="18"/>
@@ -2225,8 +2228,8 @@
       <c r="O32" s="17"/>
       <c r="P32" s="17"/>
       <c r="Q32" s="18"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="53"/>
+      <c r="R32" s="46"/>
+      <c r="S32" s="47"/>
       <c r="T32" s="17"/>
       <c r="U32" s="17"/>
       <c r="V32" s="18"/>
@@ -2260,8 +2263,8 @@
       <c r="P33" s="17"/>
       <c r="Q33" s="18"/>
       <c r="R33" s="16"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="53"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="47"/>
       <c r="U33" s="17"/>
       <c r="V33" s="18"/>
       <c r="W33" s="16"/>
@@ -2298,8 +2301,8 @@
       <c r="T34" s="17"/>
       <c r="U34" s="17"/>
       <c r="V34" s="18"/>
-      <c r="W34" s="52"/>
-      <c r="X34" s="53"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="47"/>
       <c r="Y34" s="17"/>
       <c r="Z34" s="17"/>
       <c r="AA34" s="18"/>
@@ -2323,7 +2326,7 @@
       <c r="K35" s="17"/>
       <c r="L35" s="18"/>
       <c r="M35" s="16"/>
-      <c r="N35" s="56"/>
+      <c r="N35" s="50"/>
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="Q35" s="18"/>
@@ -2361,8 +2364,8 @@
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
       <c r="Q36" s="18"/>
-      <c r="R36" s="46"/>
-      <c r="S36" s="56"/>
+      <c r="R36" s="40"/>
+      <c r="S36" s="50"/>
       <c r="T36" s="17"/>
       <c r="U36" s="17"/>
       <c r="V36" s="18"/>
@@ -2400,8 +2403,8 @@
       <c r="T37" s="17"/>
       <c r="U37" s="17"/>
       <c r="V37" s="18"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="60"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="54"/>
       <c r="Y37" s="17"/>
       <c r="Z37" s="17"/>
       <c r="AA37" s="18"/>
@@ -2419,7 +2422,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
       <c r="G38" s="15"/>
-      <c r="H38" s="45"/>
+      <c r="H38" s="39"/>
       <c r="I38" s="17"/>
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
@@ -2468,8 +2471,8 @@
       <c r="T39" s="17"/>
       <c r="U39" s="17"/>
       <c r="V39" s="18"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="59"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="53"/>
       <c r="Y39" s="17"/>
       <c r="Z39" s="17"/>
       <c r="AA39" s="18"/>
@@ -2491,8 +2494,8 @@
       <c r="I40" s="17"/>
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="16"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="46"/>
       <c r="N40" s="17"/>
       <c r="O40" s="17"/>
       <c r="P40" s="17"/>
@@ -2525,7 +2528,7 @@
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
-      <c r="L41" s="47"/>
+      <c r="L41" s="41"/>
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
       <c r="O41" s="17"/>
@@ -2578,8 +2581,8 @@
       <c r="V42" s="18"/>
       <c r="W42" s="16"/>
       <c r="X42" s="17"/>
-      <c r="Y42" s="48"/>
-      <c r="Z42" s="48"/>
+      <c r="Y42" s="42"/>
+      <c r="Z42" s="42"/>
       <c r="AA42" s="18"/>
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.3">
@@ -2618,8 +2621,8 @@
       <c r="V43" s="18"/>
       <c r="W43" s="16"/>
       <c r="X43" s="17"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="48"/>
+      <c r="Y43" s="42"/>
+      <c r="Z43" s="42"/>
       <c r="AA43" s="18"/>
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.3">
@@ -2652,7 +2655,7 @@
       <c r="X44" s="17"/>
       <c r="Y44" s="17"/>
       <c r="Z44" s="17"/>
-      <c r="AA44" s="47"/>
+      <c r="AA44" s="41"/>
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B45" s="12"/>
@@ -2684,7 +2687,7 @@
       <c r="X45" s="17"/>
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
-      <c r="AA45" s="47"/>
+      <c r="AA45" s="41"/>
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B46" s="12"/>
@@ -2826,10 +2829,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="43"/>
+      <c r="B1" s="60"/>
       <c r="C1" s="30" t="s">
         <v>78</v>
       </c>

--- a/DOCS/PPROG-25_26-DiagramaGantt-I4.xlsx
+++ b/DOCS/PPROG-25_26-DiagramaGantt-I4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\608jo\Documents\GitHub\PPROGF\DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2999CB6-5927-4C5B-B21F-9F0C3712F48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F753AB6-E929-4FE9-8044-C9B507542CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,7 +726,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -890,6 +890,9 @@
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -908,7 +911,7 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1186,80 +1189,80 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58" t="s">
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="58"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="59"/>
+      <c r="AA4" s="59"/>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="59" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59" t="s">
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="59" t="s">
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="S5" s="59"/>
-      <c r="T5" s="59"/>
-      <c r="U5" s="59"/>
-      <c r="V5" s="59"/>
-      <c r="W5" s="59" t="s">
+      <c r="S5" s="60"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="60"/>
+      <c r="V5" s="60"/>
+      <c r="W5" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="X5" s="59"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="59"/>
+      <c r="X5" s="60"/>
+      <c r="Y5" s="60"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="60"/>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B6" s="55"/>
-      <c r="C6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1350,7 +1353,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
+      <c r="L7" s="62"/>
       <c r="M7" s="38"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
@@ -2494,7 +2497,7 @@
       <c r="I40" s="17"/>
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
-      <c r="L40" s="61"/>
+      <c r="L40" s="55"/>
       <c r="M40" s="46"/>
       <c r="N40" s="17"/>
       <c r="O40" s="17"/>
@@ -2829,10 +2832,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="60"/>
+      <c r="B1" s="61"/>
       <c r="C1" s="30" t="s">
         <v>78</v>
       </c>
